--- a/data/trans_dic/P0901-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,15</t>
+          <t>5,73; 10,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,99</t>
+          <t>4,0; 8,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,29</t>
+          <t>6,93; 12,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,01</t>
+          <t>6,14; 11,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 17,27</t>
+          <t>9,54; 16,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,05</t>
+          <t>8,2; 16,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,53</t>
+          <t>9,0; 16,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,75</t>
+          <t>10,48; 15,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,19</t>
+          <t>7,61; 12,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,1</t>
+          <t>6,5; 10,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,42</t>
+          <t>8,6; 13,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,34</t>
+          <t>8,95; 12,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,28</t>
+          <t>3,23; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 15,58</t>
+          <t>8,73; 15,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,98</t>
+          <t>4,74; 9,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,83</t>
+          <t>7,93; 13,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,03</t>
+          <t>6,97; 13,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 16,57</t>
+          <t>8,37; 15,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,51</t>
+          <t>8,36; 15,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 17,13</t>
+          <t>11,78; 17,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,92</t>
+          <t>5,79; 9,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,46</t>
+          <t>9,55; 14,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,36</t>
+          <t>6,9; 11,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,34</t>
+          <t>10,43; 14,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,26</t>
+          <t>7,67; 12,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 17,55</t>
+          <t>11,35; 17,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,95</t>
+          <t>7,72; 13,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 17,22</t>
+          <t>3,92; 17,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 28,74</t>
+          <t>16,31; 29,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 26,53</t>
+          <t>16,29; 26,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,57</t>
+          <t>15,67; 29,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,23; 31,52</t>
+          <t>20,09; 31,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 15,34</t>
+          <t>10,36; 15,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,14</t>
+          <t>13,47; 18,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,01</t>
+          <t>10,85; 16,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 19,53</t>
+          <t>5,06; 19,49</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,71</t>
+          <t>9,39; 12,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,25</t>
+          <t>12,04; 16,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,69</t>
+          <t>9,85; 13,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,06</t>
+          <t>15,13; 19,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,32</t>
+          <t>12,07; 17,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,3</t>
+          <t>12,82; 18,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 17,66</t>
+          <t>12,53; 17,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,85</t>
+          <t>7,13; 17,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 13,79</t>
+          <t>10,88; 13,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,02; 16,41</t>
+          <t>13,18; 16,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 14,7</t>
+          <t>11,61; 14,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 17,94</t>
+          <t>11,5; 17,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 15,23</t>
+          <t>8,47; 15,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,76</t>
+          <t>10,79; 17,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,91</t>
+          <t>11,81; 17,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 22,9</t>
+          <t>15,9; 22,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,09; 19,16</t>
+          <t>12,65; 18,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,6; 31,44</t>
+          <t>24,69; 31,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,73; 28,11</t>
+          <t>21,36; 28,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,57; 28,64</t>
+          <t>18,66; 28,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 16,12</t>
+          <t>11,84; 16,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 24,68</t>
+          <t>20,14; 24,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,38</t>
+          <t>18,15; 22,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 25,41</t>
+          <t>18,42; 25,37</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,55</t>
+          <t>1,54; 5,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,08</t>
+          <t>2,79; 8,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,55</t>
+          <t>1,27; 6,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,37</t>
+          <t>1,17; 6,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,02</t>
+          <t>17,32; 21,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,11; 27,47</t>
+          <t>22,37; 27,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,03; 26,78</t>
+          <t>20,88; 26,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,49; 27,89</t>
+          <t>22,72; 27,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 18,22</t>
+          <t>14,67; 18,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,48; 23,03</t>
+          <t>18,71; 23,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,2; 21,77</t>
+          <t>17,12; 21,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,36; 21,76</t>
+          <t>17,48; 21,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 10,22</t>
+          <t>8,1; 10,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,3</t>
+          <t>10,86; 13,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 11,62</t>
+          <t>9,39; 11,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,42</t>
+          <t>9,86; 14,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,12; 17,61</t>
+          <t>15,0; 17,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,43; 22,2</t>
+          <t>19,5; 22,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 20,79</t>
+          <t>18,1; 20,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,84</t>
+          <t>15,77; 21,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 13,5</t>
+          <t>12,03; 13,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 17,45</t>
+          <t>15,59; 17,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 16,01</t>
+          <t>14,12; 15,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,95; 17,45</t>
+          <t>13,91; 17,47</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27645; 52834</t>
+          <t>27125; 51447</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17674; 39291</t>
+          <t>17496; 37318</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30011; 57013</t>
+          <t>29728; 55477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31158; 55634</t>
+          <t>31022; 56023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29067; 52963</t>
+          <t>29261; 52063</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26777; 50460</t>
+          <t>25772; 50810</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30375; 57365</t>
+          <t>31225; 58298</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45555; 70465</t>
+          <t>46894; 69954</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61921; 95172</t>
+          <t>59390; 95654</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50778; 83418</t>
+          <t>48870; 79210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68245; 104188</t>
+          <t>66713; 103427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83693; 117569</t>
+          <t>85287; 120012</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12039; 30398</t>
+          <t>11866; 29443</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37794; 65249</t>
+          <t>36544; 65789</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17402; 37654</t>
+          <t>17895; 36910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34662; 62530</t>
+          <t>35873; 60228</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26264; 48445</t>
+          <t>25922; 48877</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29085; 56025</t>
+          <t>28285; 53800</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30672; 57730</t>
+          <t>31134; 56275</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44672; 65537</t>
+          <t>45069; 66336</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42308; 73311</t>
+          <t>42755; 72837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71212; 109414</t>
+          <t>72244; 110297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51732; 85147</t>
+          <t>51706; 84444</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86039; 119681</t>
+          <t>87050; 120467</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40645; 66495</t>
+          <t>41602; 67180</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71537; 110445</t>
+          <t>71449; 109957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40640; 67607</t>
+          <t>40309; 68138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25549; 114979</t>
+          <t>26147; 114686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26350; 48228</t>
+          <t>27373; 49846</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41574; 69010</t>
+          <t>42367; 69270</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26807; 49121</t>
+          <t>26028; 48199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33770; 52613</t>
+          <t>33537; 52647</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73315; 108907</t>
+          <t>73582; 107642</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121012; 170303</t>
+          <t>119799; 166488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74139; 110135</t>
+          <t>74637; 111198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45766; 163046</t>
+          <t>42195; 162701</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>115227; 157405</t>
+          <t>116324; 157429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138257; 188321</t>
+          <t>139587; 191402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114866; 157360</t>
+          <t>113202; 160396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157952; 207465</t>
+          <t>156522; 204691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87033; 123750</t>
+          <t>86210; 125120</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>100257; 140286</t>
+          <t>98270; 141173</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104873; 145809</t>
+          <t>103466; 146541</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73026; 174446</t>
+          <t>69703; 173308</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212424; 269332</t>
+          <t>212398; 270691</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250639; 315913</t>
+          <t>253755; 316220</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>228112; 290436</t>
+          <t>229405; 290066</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>218770; 360850</t>
+          <t>231340; 361273</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29673; 53385</t>
+          <t>29682; 54091</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55385; 85584</t>
+          <t>55100; 87454</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75128; 111138</t>
+          <t>73311; 108129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74087; 108527</t>
+          <t>75374; 108388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>74446; 108945</t>
+          <t>71957; 107978</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187307; 239451</t>
+          <t>188013; 239254</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>160443; 207545</t>
+          <t>157712; 207174</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>156001; 240619</t>
+          <t>156770; 239203</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>106813; 148190</t>
+          <t>108885; 150848</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>254251; 313998</t>
+          <t>256195; 315715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241744; 304084</t>
+          <t>246590; 306300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>251080; 333980</t>
+          <t>242085; 333362</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4751; 16552</t>
+          <t>4581; 16570</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7038; 21570</t>
+          <t>7443; 22709</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3451; 15924</t>
+          <t>3645; 18066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2784; 12913</t>
+          <t>2805; 14774</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>215082; 275002</t>
+          <t>216257; 270455</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>245267; 304729</t>
+          <t>248216; 304685</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>227550; 289806</t>
+          <t>225978; 287449</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>171261; 212357</t>
+          <t>172961; 211737</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>225000; 281828</t>
+          <t>226914; 285371</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>254273; 316961</t>
+          <t>257429; 317623</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>235564; 298132</t>
+          <t>234457; 295232</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>173888; 218051</t>
+          <t>175162; 219464</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>267777; 334307</t>
+          <t>264980; 331447</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>375517; 455038</t>
+          <t>371585; 453750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323244; 393483</t>
+          <t>317751; 390451</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>326760; 486415</t>
+          <t>332655; 485761</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>510745; 595016</t>
+          <t>506665; 597116</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>689783; 788054</t>
+          <t>692183; 794443</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>636917; 734214</t>
+          <t>639379; 737408</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>564575; 745315</t>
+          <t>563822; 752844</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>793613; 897589</t>
+          <t>799583; 903060</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1083315; 1216770</t>
+          <t>1086931; 1208969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>979603; 1107599</t>
+          <t>976425; 1102140</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>969381; 1213108</t>
+          <t>966414; 1214435</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0901-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,86</t>
+          <t>5,72; 10,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,54</t>
+          <t>4,05; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,93</t>
+          <t>6,83; 13,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,09</t>
+          <t>6,07; 10,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,98</t>
+          <t>9,33; 17,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 16,16</t>
+          <t>8,07; 15,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,8</t>
+          <t>9,05; 16,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,63</t>
+          <t>10,96; 15,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,26</t>
+          <t>8,03; 12,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,54</t>
+          <t>6,65; 10,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,33</t>
+          <t>8,79; 13,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,6</t>
+          <t>8,88; 12,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,02</t>
+          <t>2,99; 7,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 15,71</t>
+          <t>8,64; 15,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,78</t>
+          <t>4,49; 9,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,32</t>
+          <t>7,65; 13,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,14</t>
+          <t>7,18; 13,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 15,92</t>
+          <t>8,4; 15,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,36; 15,12</t>
+          <t>8,27; 15,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 17,34</t>
+          <t>12,28; 17,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,86</t>
+          <t>5,7; 9,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,57</t>
+          <t>9,65; 14,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,27</t>
+          <t>7,05; 11,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,43</t>
+          <t>10,7; 14,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,39</t>
+          <t>7,58; 12,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 17,47</t>
+          <t>11,42; 17,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,06</t>
+          <t>7,6; 12,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 17,17</t>
+          <t>11,8; 18,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 29,71</t>
+          <t>15,99; 29,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 26,63</t>
+          <t>15,82; 25,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,67; 29,01</t>
+          <t>15,81; 29,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 31,54</t>
+          <t>19,89; 30,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,16</t>
+          <t>10,27; 15,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,47; 18,72</t>
+          <t>13,6; 18,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,16</t>
+          <t>10,79; 15,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 19,49</t>
+          <t>15,45; 21,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,71</t>
+          <t>9,27; 12,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,04; 16,51</t>
+          <t>12,07; 16,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,95</t>
+          <t>9,98; 13,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,13; 19,79</t>
+          <t>15,16; 19,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,52</t>
+          <t>12,17; 17,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 18,41</t>
+          <t>13,17; 18,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,74</t>
+          <t>12,49; 17,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 17,73</t>
+          <t>15,47; 19,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 13,86</t>
+          <t>10,95; 13,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,18; 16,42</t>
+          <t>12,91; 16,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,68</t>
+          <t>11,69; 14,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 17,96</t>
+          <t>15,95; 19,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 15,43</t>
+          <t>8,38; 15,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 17,13</t>
+          <t>10,73; 16,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,42</t>
+          <t>12,26; 17,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 22,87</t>
+          <t>14,64; 21,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 18,99</t>
+          <t>12,73; 19,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,69; 31,42</t>
+          <t>24,74; 31,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,36; 28,06</t>
+          <t>21,51; 28,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 28,47</t>
+          <t>24,59; 29,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,41</t>
+          <t>11,95; 16,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 24,82</t>
+          <t>20,03; 24,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 22,54</t>
+          <t>17,98; 22,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,42; 25,37</t>
+          <t>21,24; 25,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,56</t>
+          <t>1,56; 5,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,51</t>
+          <t>2,55; 8,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,29</t>
+          <t>1,23; 5,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,14</t>
+          <t>1,17; 5,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 21,66</t>
+          <t>17,44; 21,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,37; 27,47</t>
+          <t>22,13; 27,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,88; 26,57</t>
+          <t>21,15; 26,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,72; 27,81</t>
+          <t>22,35; 27,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 18,45</t>
+          <t>14,67; 18,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,08</t>
+          <t>18,48; 22,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,56</t>
+          <t>17,09; 21,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 21,91</t>
+          <t>17,83; 21,98</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 10,14</t>
+          <t>8,08; 10,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,86; 13,26</t>
+          <t>10,89; 13,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,53</t>
+          <t>9,47; 11,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,86; 14,4</t>
+          <t>12,41; 14,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,0; 17,68</t>
+          <t>15,05; 17,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,5; 22,38</t>
+          <t>19,42; 22,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,88</t>
+          <t>18,14; 20,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 21,05</t>
+          <t>19,71; 22,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,03; 13,58</t>
+          <t>11,96; 13,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 17,34</t>
+          <t>15,56; 17,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,12; 15,93</t>
+          <t>14,16; 16,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,47</t>
+          <t>16,53; 18,18</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42142</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>64962</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99961</t>
+          <t>109342</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27125; 51447</t>
+          <t>27122; 51541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17496; 37318</t>
+          <t>17714; 38516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29728; 55477</t>
+          <t>29326; 56307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31022; 56023</t>
+          <t>33434; 58371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29261; 52063</t>
+          <t>28609; 52606</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25772; 50810</t>
+          <t>25368; 49370</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31225; 58298</t>
+          <t>31397; 57346</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46894; 69954</t>
+          <t>53547; 77849</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59390; 95654</t>
+          <t>62638; 94988</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48870; 79210</t>
+          <t>49965; 82151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66713; 103427</t>
+          <t>68233; 104924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85287; 120012</t>
+          <t>92277; 128823</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54786</t>
+          <t>63172</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>101870</t>
+          <t>112539</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11866; 29443</t>
+          <t>10962; 29155</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36544; 65789</t>
+          <t>36172; 65335</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17895; 36910</t>
+          <t>16922; 36121</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35873; 60228</t>
+          <t>36957; 64556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25922; 48877</t>
+          <t>26687; 50323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28285; 53800</t>
+          <t>28391; 53803</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31134; 56275</t>
+          <t>30794; 58033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45069; 66336</t>
+          <t>51944; 75107</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42755; 72837</t>
+          <t>42106; 71215</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72244; 110297</t>
+          <t>73030; 113026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51706; 84444</t>
+          <t>52823; 85837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87050; 120467</t>
+          <t>96964; 132448</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>71598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109870</t>
+          <t>118293</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41602; 67180</t>
+          <t>41112; 67013</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71449; 109957</t>
+          <t>71853; 110288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40309; 68138</t>
+          <t>39670; 67725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26147; 114686</t>
+          <t>55604; 88661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27373; 49846</t>
+          <t>26830; 48881</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42367; 69270</t>
+          <t>41152; 67098</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26028; 48199</t>
+          <t>26267; 49817</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33537; 52647</t>
+          <t>37302; 58050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73582; 107642</t>
+          <t>72949; 107573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119799; 166488</t>
+          <t>120936; 167341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74637; 111198</t>
+          <t>74256; 109570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42195; 162701</t>
+          <t>101746; 139001</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180644</t>
+          <t>196465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>132522</t>
+          <t>150761</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>313166</t>
+          <t>347225</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116324; 157429</t>
+          <t>114796; 157079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>139587; 191402</t>
+          <t>139836; 189436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113202; 160396</t>
+          <t>114703; 158044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156522; 204691</t>
+          <t>171509; 222961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86210; 125120</t>
+          <t>86959; 124422</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>98270; 141173</t>
+          <t>100966; 140987</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>103466; 146541</t>
+          <t>103138; 148025</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69703; 173308</t>
+          <t>133171; 170902</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212398; 270691</t>
+          <t>213727; 272161</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253755; 316220</t>
+          <t>248632; 316843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229405; 290066</t>
+          <t>230869; 291509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>231340; 361273</t>
+          <t>317642; 379323</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91350</t>
+          <t>99011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>207300</t>
+          <t>224197</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>298650</t>
+          <t>323208</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29682; 54091</t>
+          <t>29373; 53967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55100; 87454</t>
+          <t>54805; 86322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73311; 108129</t>
+          <t>76103; 111483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75374; 108388</t>
+          <t>82975; 120198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71957; 107978</t>
+          <t>72430; 108367</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>188013; 239254</t>
+          <t>188399; 241447</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>157712; 207174</t>
+          <t>158760; 207608</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>156770; 239203</t>
+          <t>204069; 245146</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>108885; 150848</t>
+          <t>109864; 151880</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256195; 315715</t>
+          <t>254764; 313600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>246590; 306300</t>
+          <t>244294; 303008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>242085; 333362</t>
+          <t>296646; 350570</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>191132</t>
+          <t>208824</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>197225</t>
+          <t>214764</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4581; 16570</t>
+          <t>4638; 16192</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7443; 22709</t>
+          <t>6809; 21708</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3645; 18066</t>
+          <t>3543; 15713</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2805; 14774</t>
+          <t>2764; 12820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>216257; 270455</t>
+          <t>217770; 272180</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>248216; 304685</t>
+          <t>245554; 304161</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>225978; 287449</t>
+          <t>228831; 287886</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>172961; 211737</t>
+          <t>188736; 230692</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>226914; 285371</t>
+          <t>226980; 282802</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257429; 317623</t>
+          <t>254387; 315038</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>234457; 295232</t>
+          <t>234009; 297294</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>175162; 219464</t>
+          <t>192786; 237684</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>435187</t>
+          <t>466760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>685554</t>
+          <t>758611</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1120742</t>
+          <t>1225371</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>264980; 331447</t>
+          <t>264191; 331914</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>371585; 453750</t>
+          <t>372736; 456293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>317751; 390451</t>
+          <t>320494; 390262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>332655; 485761</t>
+          <t>427002; 508275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>506665; 597116</t>
+          <t>508384; 596241</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>692183; 794443</t>
+          <t>689302; 787351</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>639379; 737408</t>
+          <t>640466; 740016</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>563822; 752844</t>
+          <t>716117; 800230</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>799583; 903060</t>
+          <t>795151; 904490</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1086931; 1208969</t>
+          <t>1084814; 1222058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>976425; 1102140</t>
+          <t>979201; 1112628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>966414; 1214435</t>
+          <t>1169560; 1285823</t>
         </is>
       </c>
     </row>
